--- a/data/trans_camb/IP2004-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 3,73</t>
+          <t>-3,63; 3,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 6,07</t>
+          <t>-2,96; 6,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,7; -1,38</t>
+          <t>-6,82; -1,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 5,31</t>
+          <t>-3,01; 4,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,38</t>
+          <t>-4,06; 2,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,65</t>
+          <t>-4,55; 2,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,22</t>
+          <t>-2,19; 3,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,98</t>
+          <t>-2,6; 2,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -0,26</t>
+          <t>-4,42; -0,18</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,22; 219,54</t>
+          <t>-75,49; 245,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,53; 365,04</t>
+          <t>-68,73; 350,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,87; 274,35</t>
+          <t>-64,07; 236,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,23; 144,65</t>
+          <t>-83,54; 146,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,0; 150,18</t>
+          <t>-87,51; 128,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,82; 124,49</t>
+          <t>-49,64; 146,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,18; 124,92</t>
+          <t>-57,02; 122,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,41; 7,49</t>
+          <t>-91,39; 18,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 1,04</t>
+          <t>-5,04; 1,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,4</t>
+          <t>-5,35; 0,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 1,35</t>
+          <t>-4,9; 1,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,66</t>
+          <t>-4,59; 0,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 0,07</t>
+          <t>-4,94; -0,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 2,34</t>
+          <t>-3,58; 2,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 0,09</t>
+          <t>-3,88; -0,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,2; -0,62</t>
+          <t>-4,33; -0,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,71</t>
+          <t>-3,47; 0,83</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-74,83; 52,97</t>
+          <t>-78,03; 56,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-82,81; 31,99</t>
+          <t>-82,22; 44,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-82,02; 54,44</t>
+          <t>-78,19; 58,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-85,6; 57,41</t>
+          <t>-85,71; 38,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-91,81; 32,11</t>
+          <t>-92,18; 21,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,35; 122,62</t>
+          <t>-71,72; 107,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,23; 5,94</t>
+          <t>-73,35; 3,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,75; -14,05</t>
+          <t>-80,54; -10,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,21; 29,35</t>
+          <t>-65,51; 34,76</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 1,4</t>
+          <t>-5,34; 1,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 1,85</t>
+          <t>-4,52; 1,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; -0,58</t>
+          <t>-5,98; -0,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 1,3</t>
+          <t>-4,8; 1,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 0,24</t>
+          <t>-5,19; 0,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 1,29</t>
+          <t>-4,7; 1,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 0,51</t>
+          <t>-4,02; 0,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,23</t>
+          <t>-3,96; 0,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,34; -0,45</t>
+          <t>-4,42; -0,25</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-91,91; 103,47</t>
+          <t>-90,19; 100,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-83,63; 106,25</t>
+          <t>-80,57; 132,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -8,98</t>
+          <t>-100,0; -6,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 146,89</t>
+          <t>-100,0; 187,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 67,95</t>
+          <t>-100,0; 74,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,48; 116,68</t>
+          <t>-87,68; 118,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,25; 31,79</t>
+          <t>-79,19; 40,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,01; 20,96</t>
+          <t>-79,22; 20,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-86,09; -12,35</t>
+          <t>-87,21; 7,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 5,57</t>
+          <t>-0,72; 5,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,86</t>
+          <t>-2,48; 3,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 0,89</t>
+          <t>-3,91; 0,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 2,69</t>
+          <t>-2,53; 2,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,24</t>
+          <t>-3,36; 1,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,45</t>
+          <t>-2,87; 2,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,43</t>
+          <t>-0,79; 3,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,53</t>
+          <t>-2,12; 1,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,93</t>
+          <t>-2,59; 0,85</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,17; 570,92</t>
+          <t>-37,84; 572,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-75,56; 278,82</t>
+          <t>-72,36; 411,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-75,17; 300,64</t>
+          <t>-73,82; 331,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-89,01; 145,65</t>
+          <t>-88,42; 189,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-77,29; 264,77</t>
+          <t>-84,09; 277,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,65; 260,26</t>
+          <t>-31,04; 247,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 115,86</t>
+          <t>-66,31; 130,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-80,57; 85,33</t>
+          <t>-81,03; 89,78</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,34</t>
+          <t>-1,89; 1,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,97</t>
+          <t>-2,12; 1,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; -1,07</t>
+          <t>-3,59; -0,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,8</t>
+          <t>-2,18; 0,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,88; -0,39</t>
+          <t>-2,85; -0,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,51</t>
+          <t>-2,38; 0,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,5</t>
+          <t>-1,66; 0,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,06; -0,02</t>
+          <t>-2,1; -0,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; -0,55</t>
+          <t>-2,69; -0,56</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 50,94</t>
+          <t>-45,27; 48,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 36,35</t>
+          <t>-49,18; 42,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-84,58; -29,27</t>
+          <t>-83,86; -28,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-54,11; 35,67</t>
+          <t>-55,97; 34,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-71,9; -9,91</t>
+          <t>-72,04; -6,62</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-57,81; 22,01</t>
+          <t>-60,09; 19,8</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-40,92; 20,62</t>
+          <t>-43,17; 20,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 2,49</t>
+          <t>-54,02; -3,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-66,06; -17,16</t>
+          <t>-65,66; -19,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2004-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 3,91</t>
+          <t>-3,69; 3,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 6,04</t>
+          <t>-2,89; 6,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,82; -1,47</t>
+          <t>-6,85; -1,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 4,68</t>
+          <t>-2,36; 5,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 2,7</t>
+          <t>-4,05; 2,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 2,41</t>
+          <t>-4,23; 2,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 3,33</t>
+          <t>-2,38; 2,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,85</t>
+          <t>-2,32; 3,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,42; -0,18</t>
+          <t>-4,5; -0,21</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,49; 245,78</t>
+          <t>-70,41; 210,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-68,73; 350,27</t>
+          <t>-62,06; 381,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-64,07; 236,58</t>
+          <t>-52,2; 277,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-83,54; 146,24</t>
+          <t>-78,78; 167,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,51; 128,37</t>
+          <t>-87,22; 120,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,64; 146,23</t>
+          <t>-53,18; 122,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,02; 122,26</t>
+          <t>-52,61; 126,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,39; 18,14</t>
+          <t>-91,34; 7,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1,01</t>
+          <t>-4,97; 0,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 0,67</t>
+          <t>-5,34; 0,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 1,25</t>
+          <t>-4,82; 1,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,59</t>
+          <t>-4,63; 0,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; -0,05</t>
+          <t>-5,23; 0,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,14</t>
+          <t>-3,83; 2,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; -0,07</t>
+          <t>-3,79; 0,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -0,6</t>
+          <t>-4,22; -0,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,83</t>
+          <t>-3,42; 0,69</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-78,03; 56,67</t>
+          <t>-77,93; 39,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-82,22; 44,97</t>
+          <t>-82,44; 33,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,19; 58,83</t>
+          <t>-78,47; 66,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-85,71; 38,31</t>
+          <t>-87,34; 42,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-92,18; 21,45</t>
+          <t>-93,12; 24,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,72; 107,05</t>
+          <t>-74,46; 121,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-73,35; 3,57</t>
+          <t>-72,6; 3,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,54; -10,96</t>
+          <t>-79,39; -7,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,51; 34,76</t>
+          <t>-64,62; 27,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 1,25</t>
+          <t>-5,12; 1,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 1,72</t>
+          <t>-4,57; 1,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,98; -0,71</t>
+          <t>-6,49; -0,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 1,43</t>
+          <t>-4,62; 1,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 0,51</t>
+          <t>-4,96; 0,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 1,44</t>
+          <t>-4,38; 1,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 0,45</t>
+          <t>-4,11; 0,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,26</t>
+          <t>-3,85; 0,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,42; -0,25</t>
+          <t>-4,65; -0,44</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-90,19; 100,97</t>
+          <t>-88,25; 90,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-80,57; 132,29</t>
+          <t>-82,0; 127,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -6,78</t>
+          <t>-100,0; -19,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 187,96</t>
+          <t>-91,45; 138,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 74,7</t>
+          <t>-100,0; 91,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,68; 118,73</t>
+          <t>-87,13; 146,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-79,19; 40,06</t>
+          <t>-84,66; 32,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,22; 20,27</t>
+          <t>-79,85; 21,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-87,21; 7,39</t>
+          <t>-87,61; -7,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 5,52</t>
+          <t>-0,47; 5,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,11</t>
+          <t>-2,6; 2,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,95</t>
+          <t>-3,62; 1,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,69</t>
+          <t>-2,46; 2,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,45</t>
+          <t>-3,48; 1,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,36</t>
+          <t>-3,12; 2,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,22</t>
+          <t>-1,13; 3,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,43</t>
+          <t>-1,94; 1,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,85</t>
+          <t>-2,49; 0,99</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 572,07</t>
+          <t>-25,5; 752,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-72,36; 411,44</t>
+          <t>-76,41; 410,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-73,82; 331,6</t>
+          <t>-72,6; 267,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,42; 189,68</t>
+          <t>-87,91; 181,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-84,09; 277,82</t>
+          <t>-84,65; 231,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,04; 247,52</t>
+          <t>-37,21; 238,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-66,31; 130,43</t>
+          <t>-63,49; 109,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-81,03; 89,78</t>
+          <t>-79,2; 99,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,33</t>
+          <t>-1,83; 1,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,02</t>
+          <t>-2,33; 0,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,87</t>
+          <t>-3,58; -0,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,84</t>
+          <t>-2,24; 0,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,85; -0,28</t>
+          <t>-2,89; -0,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,51</t>
+          <t>-2,32; 0,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,59</t>
+          <t>-1,58; 0,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,1; -0,15</t>
+          <t>-2,18; -0,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,69; -0,56</t>
+          <t>-2,57; -0,53</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,27; 48,72</t>
+          <t>-43,62; 62,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 42,93</t>
+          <t>-52,41; 35,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,86; -28,78</t>
+          <t>-83,07; -26,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-55,97; 34,86</t>
+          <t>-57,38; 38,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-72,04; -6,62</t>
+          <t>-73,01; -4,54</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-60,09; 19,8</t>
+          <t>-59,35; 26,08</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-43,17; 20,96</t>
+          <t>-40,86; 23,97</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-54,02; -3,87</t>
+          <t>-54,36; -0,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-65,66; -19,61</t>
+          <t>-66,2; -18,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2004-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,87</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,82</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,23</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-3,49</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,82</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,23</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,4</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-2,33</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 3,96</t>
+          <t>-2,77; 5,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 6,08</t>
+          <t>-4,09; 2,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,85; -1,45</t>
+          <t>-4,35; 2,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 5,34</t>
+          <t>-3,6; 3,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 2,74</t>
+          <t>-2,61; 6,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 2,09</t>
+          <t>-6,7; -1,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,92</t>
+          <t>-2,52; 3,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 3,06</t>
+          <t>-2,37; 2,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,5; -0,21</t>
+          <t>-4,58; -0,35</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24,02%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-22,48%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-32,97%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-2,98%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>35,21%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24,02%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-22,48%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-33,79%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,19%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-63,35%</t>
+          <t>-65,33%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-70,41; 210,27</t>
+          <t>-60,87; 274,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,06; 381,57</t>
+          <t>-82,23; 144,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>-85,62; 165,62</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-75,22; 219,54</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>-62,53; 365,04</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-52,2; 277,54</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-78,78; 167,06</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-87,22; 120,82</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,18; 122,42</t>
+          <t>-52,82; 124,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,61; 126,79</t>
+          <t>-54,18; 124,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,34; 7,04</t>
+          <t>-91,53; 7,22</t>
         </is>
       </c>
     </row>
@@ -840,39 +840,39 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,87</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,28</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,04</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,86</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-2,33</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,89</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-1,65</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>-1,87</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,28</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,88</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-1,87</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>-2,31</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,36</t>
+          <t>-1,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 0,98</t>
+          <t>-4,47; 0,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,63</t>
+          <t>-4,97; 0,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,47</t>
+          <t>-3,74; 1,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,58</t>
+          <t>-4,73; 1,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 0,09</t>
+          <t>-5,34; 0,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 2,14</t>
+          <t>-4,92; 1,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 0,03</t>
+          <t>-3,99; 0,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -0,46</t>
+          <t>-4,2; -0,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 0,69</t>
+          <t>-3,33; 0,72</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-51,73%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-63,11%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-28,81%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-41,03%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-51,49%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-41,84%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-51,73%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-63,11%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-24,19%</t>
+          <t>-36,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-33,47%</t>
+          <t>-33,2%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,93; 39,23</t>
+          <t>-85,6; 57,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-82,44; 33,84</t>
+          <t>-91,81; 32,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,47; 66,85</t>
+          <t>-75,57; 114,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-87,34; 42,15</t>
+          <t>-74,83; 52,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-93,12; 24,57</t>
+          <t>-82,81; 31,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,46; 121,42</t>
+          <t>-80,48; 71,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,6; 3,78</t>
+          <t>-74,23; 5,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,39; -7,04</t>
+          <t>-80,75; -14,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-64,62; 27,5</t>
+          <t>-65,8; 28,34</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,05</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,24</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,76</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,24</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,98</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,6</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,05</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-2,82</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-2,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 1,42</t>
+          <t>-4,66; 1,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 1,99</t>
+          <t>-5,33; 0,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,49; -0,76</t>
+          <t>-4,32; 1,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 1,34</t>
+          <t>-5,21; 1,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 0,46</t>
+          <t>-4,66; 1,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 1,45</t>
+          <t>-6,04; -0,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 0,5</t>
+          <t>-3,88; 0,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,26</t>
+          <t>-3,77; 0,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,65; -0,44</t>
+          <t>-4,14; -0,1</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-49,53%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-63,25%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-38,16%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-46,3%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-32,74%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-78,53%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-49,53%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-63,25%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-43,22%</t>
+          <t>-74,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-62,36%</t>
+          <t>-57,08%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-88,25; 90,75</t>
+          <t>-100,0; 146,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,0; 127,41</t>
+          <t>-100,0; 67,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -19,46</t>
+          <t>-88,31; 143,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-91,45; 138,87</t>
+          <t>-91,91; 103,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 91,53</t>
+          <t>-83,63; 106,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,13; 146,71</t>
+          <t>-96,37; 10,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-84,66; 32,36</t>
+          <t>-81,25; 31,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,85; 21,86</t>
+          <t>-79,01; 20,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-87,61; -7,64</t>
+          <t>-84,47; 1,5</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,83</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,33</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,22</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,31</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>-0,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 5,72</t>
+          <t>-2,5; 2,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,89</t>
+          <t>-3,42; 1,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 1,09</t>
+          <t>-2,45; 2,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,54</t>
+          <t>-0,72; 5,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 1,57</t>
+          <t>-2,33; 2,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 2,1</t>
+          <t>-3,6; 0,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,22</t>
+          <t>-0,78; 3,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,37</t>
+          <t>-2,09; 1,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,99</t>
+          <t>-2,49; 0,88</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-36,18%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-14,3%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>104,84%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>14,82%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-65,93%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-36,18%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-13,41%</t>
+          <t>-64,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-37,59%</t>
+          <t>-38,31%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 752,95</t>
+          <t>-75,17; 300,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,41; 410,64</t>
+          <t>-89,01; 145,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>-76,67; 281,26</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>-39,17; 570,92</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>-75,56; 278,82</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-72,6; 267,05</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-87,91; 181,27</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-84,65; 231,25</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,21; 238,49</t>
+          <t>-29,65; 260,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-63,49; 109,45</t>
+          <t>-65,43; 115,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-79,2; 99,03</t>
+          <t>-80,06; 92,87</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,53</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,9</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-0,26</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,61</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,26</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,53</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>-2,15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,49</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,52</t>
+          <t>-2,1; 0,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,93</t>
+          <t>-2,88; -0,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; -0,88</t>
+          <t>-2,27; 0,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,89</t>
+          <t>-1,85; 1,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,89; -0,22</t>
+          <t>-2,29; 0,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,59</t>
+          <t>-3,76; -0,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,64</t>
+          <t>-1,61; 0,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; -0,06</t>
+          <t>-2,06; -0,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -0,53</t>
+          <t>-2,47; -0,46</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-22,98%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-48,4%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-28,37%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-7,7%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-17,67%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-65,99%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-22,98%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-48,4%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-27,92%</t>
+          <t>-62,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-46,55%</t>
+          <t>-45,34%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 62,47</t>
+          <t>-54,11; 35,67</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-52,41; 35,3</t>
+          <t>-71,9; -9,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,07; -26,95</t>
+          <t>-57,99; 19,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-57,38; 38,24</t>
+          <t>-43,6; 50,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-73,01; -4,54</t>
+          <t>-51,94; 36,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-59,35; 26,08</t>
+          <t>-83,11; -18,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-40,86; 23,97</t>
+          <t>-40,92; 20,62</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-54,36; -0,63</t>
+          <t>-54,62; 2,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-66,2; -18,78</t>
+          <t>-64,98; -14,68</t>
         </is>
       </c>
     </row>
